--- a/backlog.xlsx
+++ b/backlog.xlsx
@@ -758,7 +758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.85546875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1482,7 +1482,6 @@
           <t>todo</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Strict JSON-driven simulation configuration loader / validator</t>
@@ -1491,6 +1490,44 @@
       <c r="H19" t="inlineStr">
         <is>
           <t>Load simulation config from one JSON source and throw hard errors for ill-defined satellite, torque policy, and camera specs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BUG-004</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>todo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>MPO agent spams take-picture; budget early-stop blocks learning</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Notebook 08: agent fires shutter every step, exhausts capture budget, episode truncates early (early_stop_on_budget). Full-orbit rollouts never complete; learning signal collapsed. Fix: shutter action bias/exploration, reward for wasted shutters, action masking when budget low, or train-phase early-stop policy.</t>
         </is>
       </c>
     </row>
